--- a/AAII_Financials/Yearly/MSADY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MSADY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
   <si>
     <t>MSADY</t>
   </si>
@@ -714,7 +714,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>46033600</v>
+        <v>42881100</v>
       </c>
       <c r="E8" s="3">
         <v>42973400</v>
@@ -747,7 +747,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>32904200</v>
+        <v>37172300</v>
       </c>
       <c r="E9" s="3">
         <v>30581100</v>
@@ -780,7 +780,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>13129300</v>
+        <v>5708800</v>
       </c>
       <c r="E10" s="3">
         <v>12392400</v>
@@ -893,8 +893,8 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>427600</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E14" s="3">
         <v>144300</v>
@@ -927,7 +927,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>727800</v>
+        <v>650300</v>
       </c>
       <c r="E15" s="3">
         <v>814100</v>
@@ -972,7 +972,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>38890600</v>
+        <v>38345500</v>
       </c>
       <c r="E17" s="3">
         <v>36691000</v>
@@ -1005,7 +1005,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>7143000</v>
+        <v>4535600</v>
       </c>
       <c r="E18" s="3">
         <v>6282400</v>
@@ -1086,7 +1086,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>7870700</v>
+        <v>5185900</v>
       </c>
       <c r="E21" s="3">
         <v>7096500</v>
@@ -1119,7 +1119,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>97700</v>
+        <v>111100</v>
       </c>
       <c r="E22" s="3">
         <v>78700</v>
@@ -1152,7 +1152,7 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>6617700</v>
+        <v>4424500</v>
       </c>
       <c r="E23" s="3">
         <v>6059400</v>
@@ -1185,7 +1185,7 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1637500</v>
+        <v>1178500</v>
       </c>
       <c r="E24" s="3">
         <v>1407200</v>
@@ -1251,7 +1251,7 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>4980100</v>
+        <v>3246000</v>
       </c>
       <c r="E26" s="3">
         <v>4652200</v>
@@ -1284,7 +1284,7 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>4951700</v>
+        <v>3211300</v>
       </c>
       <c r="E27" s="3">
         <v>4618800</v>
@@ -1482,7 +1482,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>4951700</v>
+        <v>3211300</v>
       </c>
       <c r="E33" s="3">
         <v>4618800</v>
@@ -1548,7 +1548,7 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>4951700</v>
+        <v>3211300</v>
       </c>
       <c r="E35" s="3">
         <v>4618800</v>
@@ -1649,7 +1649,7 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>12266400</v>
+        <v>15809300</v>
       </c>
       <c r="E41" s="3">
         <v>14690000</v>
@@ -1682,7 +1682,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1520500</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
         <v>580300</v>
@@ -1714,8 +1714,8 @@
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>8</v>
+      <c r="D43" s="3">
+        <v>1726100</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>8</v>
@@ -1780,8 +1780,8 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>15995200</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>8</v>
@@ -1814,7 +1814,7 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>32549100</v>
+        <v>33530700</v>
       </c>
       <c r="E46" s="3">
         <v>33055800</v>
@@ -1847,7 +1847,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>126506000</v>
+        <v>132387700</v>
       </c>
       <c r="E47" s="3">
         <v>120611900</v>
@@ -1880,7 +1880,7 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2816600</v>
+        <v>2754600</v>
       </c>
       <c r="E48" s="3">
         <v>3048200</v>
@@ -1913,7 +1913,7 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2853600</v>
+        <v>2100400</v>
       </c>
       <c r="E49" s="3">
         <v>3192200</v>
@@ -2012,7 +2012,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>10153900</v>
+        <v>8094200</v>
       </c>
       <c r="E52" s="3">
         <v>8820200</v>
@@ -2078,7 +2078,7 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>180125200</v>
+        <v>186108300</v>
       </c>
       <c r="E54" s="3">
         <v>175236400</v>
@@ -2141,7 +2141,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>22771100</v>
+        <v>23600</v>
       </c>
       <c r="E57" s="3">
         <v>22044700</v>
@@ -2206,8 +2206,8 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>8</v>
+      <c r="D59" s="3">
+        <v>2921900</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>8</v>
@@ -2240,7 +2240,7 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>23117000</v>
+        <v>2945600</v>
       </c>
       <c r="E60" s="3">
         <v>22325900</v>
@@ -2273,7 +2273,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>6279100</v>
+        <v>9563600</v>
       </c>
       <c r="E61" s="3">
         <v>3943700</v>
@@ -2306,7 +2306,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>118482100</v>
+        <v>126591100</v>
       </c>
       <c r="E62" s="3">
         <v>120717300</v>
@@ -2438,7 +2438,7 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>149779400</v>
+        <v>145347100</v>
       </c>
       <c r="E66" s="3">
         <v>148172000</v>
@@ -2618,7 +2618,7 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>15630700</v>
+        <v>30994600</v>
       </c>
       <c r="E72" s="3">
         <v>14259300</v>
@@ -2750,7 +2750,7 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>29994100</v>
+        <v>40375000</v>
       </c>
       <c r="E76" s="3">
         <v>26715700</v>
@@ -2854,7 +2854,7 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>4951700</v>
+        <v>3211300</v>
       </c>
       <c r="E81" s="3">
         <v>4618800</v>
@@ -2902,10 +2902,10 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>630600</v>
-      </c>
-      <c r="E83" s="3">
-        <v>702600</v>
+        <v>650300</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F83" s="3">
         <v>682200</v>
@@ -3100,10 +3100,10 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>4796100</v>
-      </c>
-      <c r="E89" s="3">
-        <v>4408700</v>
+        <v>5999800</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F89" s="3">
         <v>3632700</v>
@@ -3148,10 +3148,10 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-202400</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-168300</v>
+        <v>-222300</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F91" s="3">
         <v>-151200</v>
@@ -3247,10 +3247,10 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-4383500</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-3731100</v>
+        <v>-4525100</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F94" s="3">
         <v>-1830200</v>
@@ -3298,7 +3298,7 @@
         <v>1414200</v>
       </c>
       <c r="E96" s="3">
-        <v>1272200</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
         <v>774400</v>
@@ -3427,10 +3427,10 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-812800</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-4404600</v>
+        <v>-872700</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F100" s="3">
         <v>-1530900</v>
@@ -3460,10 +3460,10 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>279100</v>
-      </c>
-      <c r="E101" s="3">
-        <v>423500</v>
+        <v>526500</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F101" s="3">
         <v>305700</v>
@@ -3493,10 +3493,10 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-121000</v>
+        <v>1128500</v>
       </c>
       <c r="E102" s="3">
-        <v>-3303500</v>
+        <v>0</v>
       </c>
       <c r="F102" s="3">
         <v>577400</v>
